--- a/samples/corpus/full/entreprise/billing-register/2026-04-10_suivi-de-facturation-clients.xlsx
+++ b/samples/corpus/full/entreprise/billing-register/2026-04-10_suivi-de-facturation-clients.xlsx
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -942,6 +942,18 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Observations</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Chantier Moreau : 2e échéance (fin de maçonnerie) à facturer.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
